--- a/data/trans_orig/P41E_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3123</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>991</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3527</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150331</t>
+          <t>150674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107706</t>
+          <t>107702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>106392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111348</t>
+          <t>111368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217824</t>
+          <t>217252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226945</t>
+          <t>226553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>34786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61758</t>
+          <t>61943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151600</t>
+          <t>151273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170186</t>
+          <t>169574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158548</t>
+          <t>158426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173740</t>
+          <t>173500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316712</t>
+          <t>316527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>339579</t>
+          <t>340169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161998</t>
+          <t>162145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168391</t>
+          <t>168353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150553</t>
+          <t>150434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160987</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316747</t>
+          <t>316436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>327590</t>
+          <t>327917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69312</t>
+          <t>69812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76691</t>
+          <t>76764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84413</t>
+          <t>84260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87603</t>
+          <t>87608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154932</t>
+          <t>155916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163734</t>
+          <t>163757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33657</t>
+          <t>33605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40375</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150932</t>
+          <t>150984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166912</t>
+          <t>166605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>115162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128292</t>
+          <t>128785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270731</t>
+          <t>271005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292350</t>
+          <t>291518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>267660</t>
+          <t>267761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277129</t>
+          <t>276954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>481967</t>
+          <t>483288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>495525</t>
+          <t>495533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>755697</t>
+          <t>755543</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>771653</t>
+          <t>771541</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42007</t>
+          <t>37132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191976</t>
+          <t>190796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95078</t>
+          <t>96460</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121589</t>
+          <t>123580</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97749</t>
+          <t>87661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>305828</t>
+          <t>303501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>398251</t>
+          <t>399431</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>548220</t>
+          <t>553095</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184680</t>
+          <t>182689</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>211191</t>
+          <t>209809</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>590667</t>
+          <t>592994</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>798746</t>
+          <t>808834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>102485</t>
+          <t>111245</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209182</t>
+          <t>214306</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>115136</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>216301</t>
+          <t>216997</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>271699</t>
+          <t>259713</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>413790</t>
+          <t>414366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1549479</t>
+          <t>1544355</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1656176</t>
+          <t>1647416</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1451005</t>
+          <t>1450309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1546794</t>
+          <t>1552170</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3012177</t>
+          <t>3011601</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3154268</t>
+          <t>3166254</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>152806</t>
+          <t>163465</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150674</t>
+          <t>161311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>305970</t>
+          <t>320473</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303396</t>
+          <t>317566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153164</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>306961</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113801</t>
+          <t>119278</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107702</t>
+          <t>113309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>109860</t>
+          <t>115570</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106392</t>
+          <t>111955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111368</t>
+          <t>117060</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>223660</t>
+          <t>234846</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217252</t>
+          <t>228979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226553</t>
+          <t>238052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116409</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>228334</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>228334</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>228334</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>34282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>48589</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38301</t>
+          <t>37115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61943</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>161408</t>
+          <t>165601</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151273</t>
+          <t>155566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169574</t>
+          <t>173408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167036</t>
+          <t>171896</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158426</t>
+          <t>162975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173500</t>
+          <t>178338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>328444</t>
+          <t>337498</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316527</t>
+          <t>325273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340169</t>
+          <t>348972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>186059</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186059</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186059</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>166392</t>
+          <t>192058</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162145</t>
+          <t>187068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168353</t>
+          <t>194178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>156476</t>
+          <t>173745</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150434</t>
+          <t>167428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160873</t>
+          <t>178548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>322868</t>
+          <t>365803</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316436</t>
+          <t>357932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>327917</t>
+          <t>371112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>188906</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>188906</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>188906</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>384264</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>384264</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>384264</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73912</t>
+          <t>81267</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69812</t>
+          <t>76102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76764</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>86665</t>
+          <t>94786</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84260</t>
+          <t>91645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87608</t>
+          <t>95841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>160577</t>
+          <t>176053</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155916</t>
+          <t>170507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163757</t>
+          <t>179653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32975</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>50558</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>41959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61720</t>
+          <t>61666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>159578</t>
+          <t>160437</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150984</t>
+          <t>151964</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166605</t>
+          <t>166844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>122589</t>
+          <t>125297</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115162</t>
+          <t>116891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128785</t>
+          <t>131842</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>282167</t>
+          <t>285734</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>271005</t>
+          <t>275468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>291518</t>
+          <t>295175</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>151123</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>151123</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>151123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>332725</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332725</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>332725</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>273679</t>
+          <t>320170</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>267761</t>
+          <t>314228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276954</t>
+          <t>323794</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>490891</t>
+          <t>343438</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>483288</t>
+          <t>335758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>495533</t>
+          <t>346530</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>764570</t>
+          <t>663608</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>755543</t>
+          <t>654826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>771541</t>
+          <t>668694</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>279037</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>279037</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>279037</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>496380</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>496380</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>496380</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>775417</t>
+          <t>674885</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>775417</t>
+          <t>674885</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>775417</t>
+          <t>674885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>119645</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>103221</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>190796</t>
+          <t>136732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>108392</t>
+          <t>124000</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96460</t>
+          <t>109886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123580</t>
+          <t>139609</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>216263</t>
+          <t>243645</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87661</t>
+          <t>219086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303501</t>
+          <t>266333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>482356</t>
+          <t>276696</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>399431</t>
+          <t>259609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553095</t>
+          <t>293120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>197877</t>
+          <t>229142</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>182689</t>
+          <t>213533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>209809</t>
+          <t>243256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>680232</t>
+          <t>505838</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>592994</t>
+          <t>483150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>808834</t>
+          <t>530397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>590227</t>
+          <t>396341</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>590227</t>
+          <t>396341</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>590227</t>
+          <t>396341</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>896495</t>
+          <t>749483</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>896495</t>
+          <t>749483</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>896495</t>
+          <t>749483</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111245</t>
+          <t>163464</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>214306</t>
+          <t>210543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115136</t>
+          <t>179746</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>216997</t>
+          <t>222327</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>387064</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>259713</t>
+          <t>356631</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>414366</t>
+          <t>418249</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1584290</t>
+          <t>1472513</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1544355</t>
+          <t>1448395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1647416</t>
+          <t>1495474</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1484199</t>
+          <t>1417339</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1450309</t>
+          <t>1395651</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1552170</t>
+          <t>1438232</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3068489</t>
+          <t>2889852</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3011601</t>
+          <t>2858667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3166254</t>
+          <t>2920285</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población que en el último año declara que sus relaciones sexuales no han sido satisfactorias para ambas partes (bastante en desacuerdo/totalmente en desacuerdo) en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
